--- a/partner_results/ncit/ClassMissingGermanLabel_ncit.xlsx
+++ b/partner_results/ncit/ClassMissingGermanLabel_ncit.xlsx
@@ -446,18 +446,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pixel [ncit]</t>
+          <t>Raman spectroscopy [ncit]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>information content entity</t>
+          <t>plan specification</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>The smallest resolvable rectangular area of an image, either on a screen or stored in memory.</t>
+          <t>Emission of electromagnetic energy with a shorter frequency (longer wavelength) than that of the incident monochromatic light. Arises from the low probability absorption of quanta with a higher energy than that required for a transition: the difference in energy is emitted as a lower frequency (energy) photon. Allows analysis of vibrational and rotational energy levels using visible incident light. [ NCI ]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -465,18 +465,18 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>zinc [ncit]</t>
+          <t>monomer [ncit]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>molecular entity</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>An element with atomic symbol Zn, atomic number 30, and atomic weight 65.39.</t>
+          <t>A chemical subunit that can undergo polymerization by bonding to other subunits.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -484,18 +484,18 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>agent [ncit]</t>
+          <t>standard deviation [ncit]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>measurement datum</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>An active power or cause (as principle, substance, physical or biological factor, etc.) that produces a specific effect.</t>
+          <t>A measure of the range of values in a set of numbers. Standard deviation is a statistic used as a measure of the dispersion or variation in a distribution, equal to the square root of the arithmetic mean of the squares of the deviations from the arithmetic mean. (ncit defined)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -503,18 +503,18 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>peak [ncit]</t>
+          <t>colorimetry [ncit]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>information content entity</t>
+          <t>plan specification</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>The most extreme possible amount or value; the highest point.</t>
+          <t>An assessment used to quantify and describe the colors within the visible spectrum of light.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -522,18 +522,18 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Raman spectroscopy [ncit]</t>
+          <t>shape [ncit]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>plan specification</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Emission of electromagnetic energy with a shorter frequency (longer wavelength) than that of the incident monochromatic light. Arises from the low probability absorption of quanta with a higher energy than that required for a transition: the difference in energy is emitted as a lower frequency (energy) photon. Allows analysis of vibrational and rotational energy levels using visible incident light. [ NCI ]</t>
+          <t>The spatial arrangement of something as distinct from its substance.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -541,18 +541,18 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mixing [ncit]</t>
+          <t>validation [ncit]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>planned process</t>
+          <t>process</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>To bring or combine together or with something else; add as an additional element or part.</t>
+          <t>The act of validating; finding or testing the truth of something.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -560,18 +560,18 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>standard deviation [ncit]</t>
+          <t>photometry [ncit]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>measurement datum</t>
+          <t>plan specification</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>A measure of the range of values in a set of numbers. Standard deviation is a statistic used as a measure of the dispersion or variation in a distribution, equal to the square root of the arithmetic mean of the squares of the deviations from the arithmetic mean. (ncit defined)</t>
+          <t>Measurement of the properties of light, especially luminous intensity.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -579,18 +579,18 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>validation [ncit]</t>
+          <t>agent [ncit]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>The act of validating; finding or testing the truth of something.</t>
+          <t>An active power or cause (as principle, substance, physical or biological factor, etc.) that produces a specific effect.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -598,18 +598,18 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>monomer [ncit]</t>
+          <t>pixel [ncit]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>molecular entity</t>
+          <t>information content entity</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>A chemical subunit that can undergo polymerization by bonding to other subunits.</t>
+          <t>The smallest resolvable rectangular area of an image, either on a screen or stored in memory.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -617,18 +617,18 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>count [ncit]</t>
+          <t>correlation [ncit]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>data item</t>
+          <t>measurement datum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Determining the number or amount of something.</t>
+          <t>The degree to which two or more quantities or events are associated, a statistical relation between two or more variables such that systematic changes in the value of one variable are accompanied by systematic changes in the others. The collelation can be described by mathematical functions  (often a linear function is used). It’s a common tool for describing simple relationships without making a statement about cause and effect.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -636,18 +636,18 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>photometry [ncit]</t>
+          <t>count [ncit]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>plan specification</t>
+          <t>data item</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Measurement of the properties of light, especially luminous intensity.</t>
+          <t>Determining the number or amount of something.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -655,7 +655,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>spectrum [ncit]</t>
+          <t>peak [ncit]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -666,7 +666,7 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>An array of entities, such as light waves or particles, ordered in accordance with the magnitudes of a common physical property, such as wavelength or mass.</t>
+          <t>The most extreme possible amount or value; the highest point.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -674,18 +674,18 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>shape [ncit]</t>
+          <t>mixing [ncit]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>planned process</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>The spatial arrangement of something as distinct from its substance.</t>
+          <t>To bring or combine together or with something else; add as an additional element or part.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -693,18 +693,18 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>correlation [ncit]</t>
+          <t>concentration [ncit]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>measurement datum</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>The degree to which two or more quantities or events are associated, a statistical relation between two or more variables such that systematic changes in the value of one variable are accompanied by systematic changes in the others. The collelation can be described by mathematical functions  (often a linear function is used). It’s a common tool for describing simple relationships without making a statement about cause and effect.</t>
+          <t>The quantity of a substance per unit volume or weight; a measure of the amount of substance present in a unit amount of mixture, particularly, the amount of solute dissolved in a solvent. The amounts can be expressed as moles, masses, volumes, or parts. (ncit defined)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -712,18 +712,18 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>colorimetry [ncit]</t>
+          <t>spectrum [ncit]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>plan specification</t>
+          <t>information content entity</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>An assessment used to quantify and describe the colors within the visible spectrum of light.</t>
+          <t>An array of entities, such as light waves or particles, ordered in accordance with the magnitudes of a common physical property, such as wavelength or mass.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -731,18 +731,18 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>concentration [ncit]</t>
+          <t>zinc [ncit]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>The quantity of a substance per unit volume or weight; a measure of the amount of substance present in a unit amount of mixture, particularly, the amount of solute dissolved in a solvent. The amounts can be expressed as moles, masses, volumes, or parts. (ncit defined)</t>
+          <t>An element with atomic symbol Zn, atomic number 30, and atomic weight 65.39.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
